--- a/farmer_forms/005_livestock_biosecurity_program_consent_form--farmer_forms.xlsx
+++ b/farmer_forms/005_livestock_biosecurity_program_consent_form--farmer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'participant',_'value':_'participant'}</t>
+          <t>participant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Participant', 'value': 'Participant'}</t>
+          <t>Participant</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'farmer',_'value':_'farmer'}</t>
+          <t>farmer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Farmer', 'value': 'Farmer'}</t>
+          <t>Farmer</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
+          <t>biosecurity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
+          <t>Biosecurity</t>
         </is>
       </c>
     </row>
@@ -1216,624 +1216,284 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>biosecurity_measures_choices</t>
+          <t>farm_map_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
+          <t>map_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
+          <t>Map 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>biosecurity_measures_choices</t>
+          <t>farm_map_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
+          <t>map_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
+          <t>Map 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>biosecurity_measures_choices</t>
+          <t>farm_map_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
+          <t>map_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
+          <t>Map 3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>biosecurity_measures_choices</t>
+          <t>farm_map_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
+          <t>map_4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
+          <t>Map 4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>farm_map_choices</t>
+          <t>farm_size_units_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'map_1',_'value':_'map_1'}</t>
+          <t>acres</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Map 1', 'value': 'Map 1'}</t>
+          <t>Acres</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>farm_map_choices</t>
+          <t>farm_size_units_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'map_2',_'value':_'map_2'}</t>
+          <t>hectares</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Map 2', 'value': 'Map 2'}</t>
+          <t>Hectares</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>farm_map_choices</t>
+          <t>farm_size_units_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'map_3',_'value':_'map_3'}</t>
+          <t>square_kilometers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Map 3', 'value': 'Map 3'}</t>
+          <t>Square Kilometers</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>farm_map_choices</t>
+          <t>farm_size_units_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'map_4',_'value':_'map_4'}</t>
+          <t>square_miles</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Map 4', 'value': 'Map 4'}</t>
+          <t>Square Miles</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>farm_size_units_choices</t>
+          <t>biosecurity_measures_1_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'acres',_'value':_'acres'}</t>
+          <t>biosecurity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Acres', 'value': 'Acres'}</t>
+          <t>Biosecurity</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>farm_size_units_choices</t>
+          <t>biosecurity_measures_1_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'hectares',_'value':_'hectares'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Hectares', 'value': 'Hectares'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>farm_size_units_choices</t>
+          <t>biosecurity_measures_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'square_kilometers',_'value':_'square_kilometers'}</t>
+          <t>biosecurity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Square Kilometers', 'value': 'Square Kilometers'}</t>
+          <t>Biosecurity</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>farm_size_units_choices</t>
+          <t>biosecurity_measures_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'square_miles',_'value':_'square_miles'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Square Miles', 'value': 'Square Miles'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>biosecurity_measures_1_choices</t>
+          <t>biosecurity_measures_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
+          <t>biosecurity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
+          <t>Biosecurity</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>biosecurity_measures_1_choices</t>
+          <t>biosecurity_measures_3_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>biosecurity_measures_1_choices</t>
+          <t>biosecurity_measures_4_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
+          <t>biosecurity</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
+          <t>Biosecurity</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>biosecurity_measures_1_choices</t>
+          <t>biosecurity_measures_4_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_1_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_1_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_2_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_2_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_3_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_3_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_3_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_3_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_3_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_3_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_4_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_4_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_4_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_4_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_4_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>biosecurity_measures_4_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'label':_'biosecurity',_'value':_'biosecurity'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'label': 'Biosecurity', 'value': 'Biosecurity'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
